--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>101219</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348125.0850001429</v>
+        <v>348125</v>
       </c>
       <c r="R2" t="n">
-        <v>6516763.848862814</v>
+        <v>6516764</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1973-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1973-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348125.0850001429</v>
+        <v>348125</v>
       </c>
       <c r="R3" t="n">
-        <v>6516763.848862814</v>
+        <v>6516764</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +844,9 @@
           <t>1973-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1973-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103041</v>
+        <v>103052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101641</v>
+        <v>101649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103052</v>
+        <v>103060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101649</v>
+        <v>101657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103060</v>
+        <v>103072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101657</v>
+        <v>101662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103072</v>
+        <v>103078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103078</v>
+        <v>103080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103080</v>
+        <v>103107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103107</v>
+        <v>103113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103113</v>
+        <v>103120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103120</v>
+        <v>103124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17693-2023 artfynd.xlsx
+++ b/artfynd/A 17693-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>57080545</v>
       </c>
       <c r="B2" t="n">
-        <v>103124</v>
+        <v>103131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>57080591</v>
       </c>
       <c r="B3" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
